--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0006.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0006.xlsx
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Chanty Bounty</t>
+          <t>Ủy Thác Chanty</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Cửa hàng</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Vật phẩm trong vùng Dodget đứt có thể bán nhanh với giá cao hơn ở cửa hàng.</t>
+          <t>Vật phẩm trong vùng nét đứt có thể bán nhanh với giá cao hơn ở cửa hàng.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Chanty Bounty</t>
+          <t>Ủy Thác Chanty</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Chanty Bounty</t>
+          <t>Ủy Thác Chanty</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>Bỏ qua</t>
         </is>
       </c>
     </row>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Chỉ số</t>
         </is>
       </c>
     </row>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Chọn Buff Cộng Hưởng</t>
+          <t>Chọn Buff Resonator</t>
         </is>
       </c>
     </row>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào vùng trống để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào vùng trống để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -29111,7 +29111,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Return Đoạn phim</t>
+          <t>Quay lại đoạn phim.</t>
         </is>
       </c>
     </row>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu khảo sát</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu khảo sát</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu khảo sát</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu khảo sát</t>
         </is>
       </c>
     </row>
